--- a/www/ig/fhir/core/CodeSystem-fr-core-cs-v2-3307.xlsx
+++ b/www/ig/fhir/core/CodeSystem-fr-core-cs-v2-3307.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="71">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-19T12:11:47+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,10 +72,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -126,7 +126,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>17</t>
+    <t>14</t>
   </si>
   <si>
     <t>Level</t>
@@ -144,18 +144,18 @@
     <t>1</t>
   </si>
   <si>
+    <t>GHT</t>
+  </si>
+  <si>
+    <t>Groupement hospitalier de territoire</t>
+  </si>
+  <si>
     <t>LEGAL-ENTITY</t>
   </si>
   <si>
     <t>Entité légale</t>
   </si>
   <si>
-    <t>GHT</t>
-  </si>
-  <si>
-    <t>Groupement hospitalier de territoire</t>
-  </si>
-  <si>
     <t>GEOGRAPHICAL-ENTITY</t>
   </si>
   <si>
@@ -168,82 +168,64 @@
     <t>Groupe privé/hospitalier</t>
   </si>
   <si>
-    <t>HEBERGEMENT</t>
-  </si>
-  <si>
-    <t>Hébergement</t>
-  </si>
-  <si>
-    <t>SOIN</t>
-  </si>
-  <si>
-    <t>Soin</t>
-  </si>
-  <si>
-    <t>ADMINISTRATIF</t>
-  </si>
-  <si>
-    <t>Administration</t>
-  </si>
-  <si>
-    <t>MEDICAL</t>
-  </si>
-  <si>
-    <t>Médical</t>
-  </si>
-  <si>
-    <t>TECHNIQUE</t>
-  </si>
-  <si>
-    <t>Technique</t>
-  </si>
-  <si>
-    <t>MEDICOTEC</t>
-  </si>
-  <si>
-    <t>medico technique (radio, scanner …)</t>
+    <t>STRUCT-INTERNE</t>
+  </si>
+  <si>
+    <t>Structure interne</t>
+  </si>
+  <si>
+    <t>SECTEUR</t>
+  </si>
+  <si>
+    <t>Secteur</t>
+  </si>
+  <si>
+    <t>DEPARTEMENT</t>
+  </si>
+  <si>
+    <t>Département</t>
+  </si>
+  <si>
+    <t>SERVICE</t>
+  </si>
+  <si>
+    <t>Service</t>
+  </si>
+  <si>
+    <t>UM</t>
+  </si>
+  <si>
+    <t>Unité médicale</t>
+  </si>
+  <si>
+    <t>UAC</t>
+  </si>
+  <si>
+    <t>Unité d'activité</t>
+  </si>
+  <si>
+    <t>POLE</t>
+  </si>
+  <si>
+    <t>Pôle</t>
+  </si>
+  <si>
+    <t>CENTRE-RESP</t>
+  </si>
+  <si>
+    <t>Centre de responsabilité</t>
+  </si>
+  <si>
+    <t>CENTRE-ACTIVITE</t>
+  </si>
+  <si>
+    <t>Centre d'activité</t>
   </si>
   <si>
     <t>UF</t>
   </si>
   <si>
     <t>Unité fonctionnelle</t>
-  </si>
-  <si>
-    <t>SERVICE</t>
-  </si>
-  <si>
-    <t>Service</t>
-  </si>
-  <si>
-    <t>UM</t>
-  </si>
-  <si>
-    <t>Unité médicale</t>
-  </si>
-  <si>
-    <t>UAC</t>
-  </si>
-  <si>
-    <t>Unité d'activité</t>
-  </si>
-  <si>
-    <t>POLE</t>
-  </si>
-  <si>
-    <t>Pôle</t>
-  </si>
-  <si>
-    <t>CENTRE-RESP</t>
-  </si>
-  <si>
-    <t>Centre de responsabilité</t>
-  </si>
-  <si>
-    <t>CENTRE-ACTIVITE</t>
-  </si>
-  <si>
-    <t>Centre d'activité</t>
   </si>
 </sst>
 </file>
@@ -561,7 +543,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -746,42 +728,6 @@
       </c>
       <c r="D15" s="2"/>
     </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="C16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="D16" s="2"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="C17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="D17" s="2"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="C18" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="D18" s="2"/>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/www/ig/fhir/core/CodeSystem-fr-core-cs-v2-3307.xlsx
+++ b/www/ig/fhir/core/CodeSystem-fr-core-cs-v2-3307.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="77">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T12:11:47+01:00</t>
+    <t>2024-09-04T10:06:33+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,10 +72,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(Work))</t>
+    <t>Interop'Santé (http://interopsante.org/)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -126,7 +126,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>14</t>
+    <t>17</t>
   </si>
   <si>
     <t>Level</t>
@@ -144,18 +144,18 @@
     <t>1</t>
   </si>
   <si>
+    <t>LEGAL-ENTITY</t>
+  </si>
+  <si>
+    <t>Entité légale</t>
+  </si>
+  <si>
     <t>GHT</t>
   </si>
   <si>
     <t>Groupement hospitalier de territoire</t>
   </si>
   <si>
-    <t>LEGAL-ENTITY</t>
-  </si>
-  <si>
-    <t>Entité légale</t>
-  </si>
-  <si>
     <t>GEOGRAPHICAL-ENTITY</t>
   </si>
   <si>
@@ -168,22 +168,46 @@
     <t>Groupe privé/hospitalier</t>
   </si>
   <si>
-    <t>STRUCT-INTERNE</t>
-  </si>
-  <si>
-    <t>Structure interne</t>
-  </si>
-  <si>
-    <t>SECTEUR</t>
-  </si>
-  <si>
-    <t>Secteur</t>
-  </si>
-  <si>
-    <t>DEPARTEMENT</t>
-  </si>
-  <si>
-    <t>Département</t>
+    <t>HEBERGEMENT</t>
+  </si>
+  <si>
+    <t>Hébergement</t>
+  </si>
+  <si>
+    <t>SOIN</t>
+  </si>
+  <si>
+    <t>Soin</t>
+  </si>
+  <si>
+    <t>ADMINISTRATIF</t>
+  </si>
+  <si>
+    <t>Administration</t>
+  </si>
+  <si>
+    <t>MEDICAL</t>
+  </si>
+  <si>
+    <t>Médical</t>
+  </si>
+  <si>
+    <t>TECHNIQUE</t>
+  </si>
+  <si>
+    <t>Technique</t>
+  </si>
+  <si>
+    <t>MEDICOTEC</t>
+  </si>
+  <si>
+    <t>medico technique (radio, scanner …)</t>
+  </si>
+  <si>
+    <t>UF</t>
+  </si>
+  <si>
+    <t>Unité fonctionnelle</t>
   </si>
   <si>
     <t>SERVICE</t>
@@ -220,12 +244,6 @@
   </si>
   <si>
     <t>Centre d'activité</t>
-  </si>
-  <si>
-    <t>UF</t>
-  </si>
-  <si>
-    <t>Unité fonctionnelle</t>
   </si>
 </sst>
 </file>
@@ -543,7 +561,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -728,6 +746,42 @@
       </c>
       <c r="D15" s="2"/>
     </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="C17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="D18" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/www/ig/fhir/core/CodeSystem-fr-core-cs-v2-3307.xlsx
+++ b/www/ig/fhir/core/CodeSystem-fr-core-cs-v2-3307.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="71">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-25T18:08:32+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,10 +72,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -126,7 +126,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>17</t>
+    <t>14</t>
   </si>
   <si>
     <t>Level</t>
@@ -144,18 +144,18 @@
     <t>1</t>
   </si>
   <si>
+    <t>GHT</t>
+  </si>
+  <si>
+    <t>Groupement hospitalier de territoire</t>
+  </si>
+  <si>
     <t>LEGAL-ENTITY</t>
   </si>
   <si>
     <t>Entité légale</t>
   </si>
   <si>
-    <t>GHT</t>
-  </si>
-  <si>
-    <t>Groupement hospitalier de territoire</t>
-  </si>
-  <si>
     <t>GEOGRAPHICAL-ENTITY</t>
   </si>
   <si>
@@ -168,82 +168,64 @@
     <t>Groupe privé/hospitalier</t>
   </si>
   <si>
-    <t>HEBERGEMENT</t>
-  </si>
-  <si>
-    <t>Hébergement</t>
-  </si>
-  <si>
-    <t>SOIN</t>
-  </si>
-  <si>
-    <t>Soin</t>
-  </si>
-  <si>
-    <t>ADMINISTRATIF</t>
-  </si>
-  <si>
-    <t>Administration</t>
-  </si>
-  <si>
-    <t>MEDICAL</t>
-  </si>
-  <si>
-    <t>Médical</t>
-  </si>
-  <si>
-    <t>TECHNIQUE</t>
-  </si>
-  <si>
-    <t>Technique</t>
-  </si>
-  <si>
-    <t>MEDICOTEC</t>
-  </si>
-  <si>
-    <t>medico technique (radio, scanner …)</t>
+    <t>STRUCT-INTERNE</t>
+  </si>
+  <si>
+    <t>Structure interne</t>
+  </si>
+  <si>
+    <t>SECTEUR</t>
+  </si>
+  <si>
+    <t>Secteur</t>
+  </si>
+  <si>
+    <t>DEPARTEMENT</t>
+  </si>
+  <si>
+    <t>Département</t>
+  </si>
+  <si>
+    <t>SERVICE</t>
+  </si>
+  <si>
+    <t>Service</t>
+  </si>
+  <si>
+    <t>UM</t>
+  </si>
+  <si>
+    <t>Unité médicale</t>
+  </si>
+  <si>
+    <t>UAC</t>
+  </si>
+  <si>
+    <t>Unité d'activité</t>
+  </si>
+  <si>
+    <t>POLE</t>
+  </si>
+  <si>
+    <t>Pôle</t>
+  </si>
+  <si>
+    <t>CENTRE-RESP</t>
+  </si>
+  <si>
+    <t>Centre de responsabilité</t>
+  </si>
+  <si>
+    <t>CENTRE-ACTIVITE</t>
+  </si>
+  <si>
+    <t>Centre d'activité</t>
   </si>
   <si>
     <t>UF</t>
   </si>
   <si>
     <t>Unité fonctionnelle</t>
-  </si>
-  <si>
-    <t>SERVICE</t>
-  </si>
-  <si>
-    <t>Service</t>
-  </si>
-  <si>
-    <t>UM</t>
-  </si>
-  <si>
-    <t>Unité médicale</t>
-  </si>
-  <si>
-    <t>UAC</t>
-  </si>
-  <si>
-    <t>Unité d'activité</t>
-  </si>
-  <si>
-    <t>POLE</t>
-  </si>
-  <si>
-    <t>Pôle</t>
-  </si>
-  <si>
-    <t>CENTRE-RESP</t>
-  </si>
-  <si>
-    <t>Centre de responsabilité</t>
-  </si>
-  <si>
-    <t>CENTRE-ACTIVITE</t>
-  </si>
-  <si>
-    <t>Centre d'activité</t>
   </si>
 </sst>
 </file>
@@ -561,7 +543,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -746,42 +728,6 @@
       </c>
       <c r="D15" s="2"/>
     </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="C16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="D16" s="2"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="C17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="D17" s="2"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="C18" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="D18" s="2"/>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
